--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -3723,12 +3723,12 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>[Incident Tracker] Bus Incident Involving Your Child - {{incident_id}}</t>
+          <t>Incident Involving Your Child - {{incident_type}} - {{incident_id}}</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Dear {{parent_name}},
+          <t>Hello,
 We are writing to inform you of an incident that occurred on {{incident_date}} involving your child, {{student_name}}, while riding {{bus_route}}.
 Incident Type: {{incident_type}}
 Severity: {{severity}}
@@ -3737,7 +3737,7 @@
 {{incident_summary}}
 Immediate actions taken:
 {{actions_taken}}
-If you have any questions or concerns, please contact {{contact_name}} at {{contact_phone}} or {{contact_email}}.
+If you have any questions or concerns, please contact INSERT NAME at PHONE# or EMAIL.
 Sincerely,
 {{sender_name}}
 {{sender_title}}
@@ -3746,7 +3746,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>parent_name, student_name, bus_route, incident_date, incident_type, severity, incident_location, incident_summary, actions_taken, contact_name, contact_phone, contact_email, sender_name, sender_title</t>
+          <t>student_name, bus_route, incident_date, incident_type, severity, incident_location, incident_summary, actions_taken, sender_name, sender_title</t>
         </is>
       </c>
     </row>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -3651,30 +3651,80 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>General notification that a workflow step requires action by the assigned role. Suitable for routine and time-sensitive steps alike.</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Action Required: {{step_name}} - {{incident_id}}</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Hello,
+A workflow step requires your attention:
+Step: {{step_name}}
+Incident: {{incident_id}}
+Severity: {{severity}}
+Assigned To: {{assigned_role}}
+Please log in to the Incident Tracker to review and complete this step.
+Thank you,
+Incident Tracker System</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>step_name, incident_id, severity, assigned_role</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ET-002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
           <t>Approval Request</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Approval</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>Sent to designated approvers when a step requires approval before proceeding.</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>Approval needed for workflow step: {{step_name}} ({{incident_id}})</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Hello,
 Your approval is needed for the following workflow step:
@@ -3689,44 +3739,44 @@
 Incident Tracker System</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>step_name, incident_id, requested_by, request_date, step_description</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>ET-002</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>ET-003</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Parent/Guardian Notification</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Notification</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Sent to parents or guardians when their child is involved in a bus incident. Used across most student-related workflows.</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Incident Involving Your Child - {{incident_type}} - {{incident_id}}</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Hello,
 We are writing to inform you of an incident that occurred on {{incident_date}} involving your child, {{student_name}}, while riding {{bus_route}}.
@@ -3744,61 +3794,9 @@
 Student Transportation Department</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H4" s="6" t="inlineStr">
         <is>
           <t>student_name, bus_route, incident_date, incident_type, severity, incident_location, incident_summary, actions_taken, sender_name, sender_title</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ET-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Urgent Action Required</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Notification</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>High-priority notification for critical or time-sensitive workflow steps.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>[URGENT] Action Required: {{step_name}} - {{incident_id}}</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>URGENT: Immediate action is required.
-Hello {{recipient_name}},
-A high-priority workflow step requires your immediate attention:
-Step: {{step_name}}
-Incident: {{incident_id}}
-Severity: {{severity}}
-Assigned To: {{assigned_role}}
-Please log in to the Incident Tracker immediately to address this matter.
-This notification was sent because the incident severity is {{severity}} and requires prompt resolution.
-Thank you,
-Incident Tracker System</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>recipient_name, step_name, incident_id, severity, assigned_role</t>
         </is>
       </c>
     </row>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -1563,12 +1563,12 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Safety Coordinator Notification</t>
+          <t>Submit Incident Report via Tablet App</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Notify safety coordinator of incident details, injuries, and any threatening behavior</t>
+          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Submit Incident Report via Tablet App</t>
+          <t>Submit Incident Report</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1601,26 +1601,10 @@
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
     </row>
     <row r="7">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -1663,12 +1663,12 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="R7" s="7" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incident Types'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflows'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$T$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Email Templates'!$A$1:$H$4</definedName>
   </definedNames>
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B30"/>
+  <dimension ref="B1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -646,50 +646,57 @@
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). In the current configuration no step references a template, but the templates remain seeded as a reusable library.</t>
+          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). Currently only WF-002 step 4 references a template ('Action Required'); the others are seeded as a reusable library.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>• Every workflow step is manually triggered (trigger_type = manual); there are no time-delay/conditional/auto-advance steps in the current configuration.</t>
+          <t>• 'notify_groups' lists the roles that should receive the step's email (comma-separated). 'notify_on_start' / 'notify_on_complete' indicate timing: notify before the step starts vs. after it completes.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>• estimated_duration / default_duration are free-text labels ('15 minutes', '2 hours'); keep as text unless you parse them into minutes.</t>
+          <t>• Every workflow step is manually triggered (trigger_type = manual); there are no time-delay/conditional/auto-advance steps in the current configuration.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>• Email template variables are listed without the surrounding {{ }} braces; the body shows the {{placeholder}} form.</t>
+          <t>• estimated_duration / default_duration are free-text labels ('15 minutes', '2 hours'); keep as text unless you parse them into minutes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>• 'Witness / Bystander Statement' (incident type + WF-006) is intentionally non-disciplinary: no parent notification or approval steps, so a student who only witnessed/helped is not flagged on a disciplinary incident.</t>
+          <t>• Email template variables are listed without the surrounding {{ }} braces; the body shows the {{placeholder}} form.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>• 'Witness / Bystander Statement' (incident type + WF-006) is intentionally non-disciplinary: no parent notification or approval steps, so a student who only witnessed/helped is not flagged on a disciplinary incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>• Severity values: Low, Medium, High, Critical.   applicable_to values: student, driver, both.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Generated by gen_seed_catalog_xlsx.py — re-run after editing the app data files to refresh.</t>
         </is>
@@ -1164,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1186,7 +1193,8 @@
     <col width="15" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1286,6 +1294,11 @@
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>notify_groups</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>additional_recipients</t>
         </is>
@@ -1350,6 +1363,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr"/>
+      <c r="U2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1426,6 +1440,7 @@
         </is>
       </c>
       <c r="T3" s="7" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1486,6 +1501,7 @@
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
+      <c r="U4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1546,6 +1562,7 @@
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="7" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1606,6 +1623,7 @@
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr"/>
       <c r="T6" s="5" t="inlineStr"/>
+      <c r="U6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1682,6 +1700,7 @@
         </is>
       </c>
       <c r="T7" s="7" t="inlineStr"/>
+      <c r="U7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1740,10 +1759,14 @@
       <c r="L8" s="5" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
-      <c r="O8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q8" s="5" t="inlineStr">
@@ -1761,7 +1784,12 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1822,6 +1850,7 @@
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr"/>
       <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1882,6 +1911,7 @@
       <c r="R10" s="5" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr"/>
       <c r="T10" s="5" t="inlineStr"/>
+      <c r="U10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1958,6 +1988,7 @@
         </is>
       </c>
       <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -2034,6 +2065,7 @@
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr"/>
+      <c r="U12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2114,6 +2146,7 @@
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -2174,6 +2207,7 @@
       <c r="R14" s="5" t="inlineStr"/>
       <c r="S14" s="5" t="inlineStr"/>
       <c r="T14" s="5" t="inlineStr"/>
+      <c r="U14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -2234,6 +2268,7 @@
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr"/>
       <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -2310,6 +2345,7 @@
         </is>
       </c>
       <c r="T16" s="5" t="inlineStr"/>
+      <c r="U16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -2370,6 +2406,7 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr"/>
       <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2450,6 +2487,7 @@
         </is>
       </c>
       <c r="T18" s="5" t="inlineStr"/>
+      <c r="U18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2510,6 +2548,7 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr"/>
       <c r="T19" s="7" t="inlineStr"/>
+      <c r="U19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2570,6 +2609,7 @@
       <c r="R20" s="5" t="inlineStr"/>
       <c r="S20" s="5" t="inlineStr"/>
       <c r="T20" s="5" t="inlineStr"/>
+      <c r="U20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -2646,6 +2686,7 @@
         </is>
       </c>
       <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2722,6 +2763,7 @@
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr"/>
+      <c r="U22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -2802,6 +2844,7 @@
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2862,6 +2905,7 @@
       <c r="R24" s="5" t="inlineStr"/>
       <c r="S24" s="5" t="inlineStr"/>
       <c r="T24" s="5" t="inlineStr"/>
+      <c r="U24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -2922,6 +2966,7 @@
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="7" t="inlineStr"/>
       <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2982,6 +3027,7 @@
       <c r="R26" s="5" t="inlineStr"/>
       <c r="S26" s="5" t="inlineStr"/>
       <c r="T26" s="5" t="inlineStr"/>
+      <c r="U26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -3042,9 +3088,10 @@
       <c r="R27" s="7" t="inlineStr"/>
       <c r="S27" s="7" t="inlineStr"/>
       <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T27"/>
+  <autoFilter ref="A1:U27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -646,7 +646,7 @@
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). Currently only WF-002 step 4 references a template ('Action Required'); the others are seeded as a reusable library.</t>
+          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). The disciplinary-review steps (WF-002/003/004/005 step 4) reference the 'Action Required' template; the other templates are seeded as a reusable library.</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1426,12 @@
       </c>
       <c r="Q3" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="R3" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -2046,12 +2046,12 @@
       <c r="O12" s="5" t="inlineStr"/>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="R12" s="5" t="inlineStr">
@@ -2124,10 +2124,14 @@
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
       <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q13" s="7" t="inlineStr">
@@ -2145,7 +2149,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
       <c r="U13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2401,10 +2409,26 @@
       <c r="M17" s="7" t="inlineStr"/>
       <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="7" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr"/>
-      <c r="Q17" s="7" t="inlineStr"/>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
       <c r="T17" s="7" t="inlineStr"/>
       <c r="U17" s="7" t="inlineStr"/>
     </row>
@@ -2465,10 +2489,14 @@
       <c r="L18" s="5" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
-      <c r="O18" s="5" t="inlineStr"/>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
       <c r="P18" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q18" s="5" t="inlineStr">
@@ -2486,7 +2514,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
       <c r="U18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2744,12 +2776,12 @@
       <c r="O22" s="5" t="inlineStr"/>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="R22" s="5" t="inlineStr">
@@ -2822,10 +2854,14 @@
       <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q23" s="7" t="inlineStr">
@@ -2843,7 +2879,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="T23" s="7" t="inlineStr"/>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
       <c r="U23" s="7" t="inlineStr"/>
     </row>
     <row r="24">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -2659,22 +2659,22 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Dispatch &amp; Safety Coordinator Alert</t>
+          <t>Submit Incident Report</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>For high-severity situations (emergency exit, wrong stop): notify dispatch and safety coordinator immediately</t>
+          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Safety Coordinator</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>10 minutes</t>
+          <t>15 minutes</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2697,26 +2697,10 @@
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
       <c r="O21" s="7" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr"/>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr"/>
       <c r="T21" s="7" t="inlineStr"/>
       <c r="U21" s="7" t="inlineStr"/>
     </row>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -2797,12 +2797,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Safety Review &amp; Disciplinary Action</t>
+          <t>Disciplinary Action Review</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Review incident severity and history. Determine if disciplinary measures are warranted.</t>
+          <t>Administrator reviews incident and determines appropriate disciplinary measures</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>20 minutes</t>
+          <t>1 hour</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -646,7 +646,7 @@
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). The disciplinary-review steps (WF-002/003/004/005 step 4) reference the 'Action Required' template; the other templates are seeded as a reusable library.</t>
+          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). The disciplinary-review steps (WF-002/003/004/005 step 4) and WF-004 step 2 (Fleet Manager Review) reference the 'Action Required' template; the other templates are seeded as a reusable library.</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,11 @@
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
-      <c r="O16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
       <c r="P16" s="5" t="inlineStr">
         <is>
           <t>TRUE</t>
@@ -2352,7 +2356,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
       <c r="U16" s="5" t="inlineStr"/>
     </row>
     <row r="17">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -2338,7 +2338,7 @@
       </c>
       <c r="P16" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="Q16" s="5" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incident Types'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflows'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Email Templates'!$A$1:$H$4</definedName>
   </definedNames>
@@ -646,7 +646,7 @@
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). The disciplinary-review steps (WF-002/003/004/005 step 4) and WF-004 step 2 (Fleet Manager Review) reference the 'Action Required' template; the other templates are seeded as a reusable library.</t>
+          <t>• 'email_template' on a step references Email Templates.name. A blank means the step sends no templated email (though notify_* flags may still be set). Several steps reference the 'Action Required' template — the disciplinary-review step 4s (WF-002/003/004/005) and WF-004 steps 2 and 5; the other templates are seeded as a reusable library.</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2582,46 +2582,70 @@
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
       <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr"/>
-      <c r="P19" s="7" t="inlineStr"/>
-      <c r="Q19" s="7" t="inlineStr"/>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="7" t="inlineStr"/>
-      <c r="T19" s="7" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
       <c r="U19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>WF-005</t>
+          <t>WF-004</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>step-1</t>
+          <t>step-6</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Immediate Safety Response</t>
+          <t>Documentation &amp; Close</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Driver addresses the safety issue, secures the situation, and documents the incident</t>
+          <t>Complete incident documentation and close case</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Safety Coordinator</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>15 minutes</t>
+          <t>20 minutes</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
@@ -2659,20 +2683,20 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>step-2</t>
+          <t>step-1</t>
         </is>
       </c>
       <c r="C21" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Submit Incident Report</t>
+          <t>Immediate Safety Response</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
+          <t>Driver addresses the safety issue, secures the situation, and documents the incident</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -2720,25 +2744,25 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>step-3</t>
+          <t>step-2</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Parent Notification</t>
+          <t>Submit Incident Report</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Contact parent/guardian to inform them of the safety violation and reinforce bus safety expectations</t>
+          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Safety Coordinator</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2766,26 +2790,10 @@
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="5" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="S22" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="P22" s="5" t="inlineStr"/>
+      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+      <c r="S22" s="5" t="inlineStr"/>
       <c r="T22" s="5" t="inlineStr"/>
       <c r="U22" s="5" t="inlineStr"/>
     </row>
@@ -2797,30 +2805,30 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>step-4</t>
+          <t>step-3</t>
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Disciplinary Action Review</t>
+          <t>Parent Notification</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Administrator reviews incident and determines appropriate disciplinary measures</t>
+          <t>Contact parent/guardian to inform them of the safety violation and reinforce bus safety expectations</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Safety Coordinator</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>1 hour</t>
+          <t>15 minutes</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -2830,14 +2838,10 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr">
         <is>
           <t>manual</t>
@@ -2846,11 +2850,7 @@
       <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
       <c r="N23" s="7" t="inlineStr"/>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
+      <c r="O23" s="7" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr">
         <is>
           <t>FALSE</t>
@@ -2868,14 +2868,10 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T23" s="7" t="inlineStr">
-        <is>
-          <t>Safety Coordinator</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr"/>
       <c r="U23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
@@ -2886,30 +2882,30 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>step-5</t>
+          <t>step-4</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Documentation &amp; Close</t>
+          <t>Disciplinary Action Review</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Complete all documentation and close the incident</t>
+          <t>Administrator reviews incident and determines appropriate disciplinary measures</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Safety Coordinator</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>10 minutes</t>
+          <t>1 hour</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
@@ -2919,10 +2915,14 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
           <t>manual</t>
@@ -2931,41 +2931,65 @@
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
-      <c r="O24" s="5" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
-      <c r="R24" s="5" t="inlineStr"/>
-      <c r="S24" s="5" t="inlineStr"/>
-      <c r="T24" s="5" t="inlineStr"/>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="R24" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="S24" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
       <c r="U24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>WF-006</t>
+          <t>WF-005</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>step-1</t>
+          <t>step-5</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Record Witness Statement</t>
+          <t>Documentation &amp; Close</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Driver or staff records the witness/bystander account of what they saw or how they helped. No fault is assigned to this student.</t>
+          <t>Complete all documentation and close the incident</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Safety Coordinator</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -3008,25 +3032,25 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>step-2</t>
+          <t>step-1</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Link to Related Incident</t>
+          <t>Record Witness Statement</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Safety coordinator reviews the statement and links it to the related disciplinary incident (e.g. the physical altercation) for context.</t>
+          <t>Driver or staff records the witness/bystander account of what they saw or how they helped. No fault is assigned to this student.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Safety Coordinator</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -3036,7 +3060,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -3069,20 +3093,20 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>step-3</t>
+          <t>step-2</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>File &amp; Close</t>
+          <t>Link to Related Incident</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>File the witness statement and close. No disciplinary measures or parent notification are required for the witness.</t>
+          <t>Safety coordinator reviews the statement and links it to the related disciplinary incident (e.g. the physical altercation) for context.</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -3092,12 +3116,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>5 minutes</t>
+          <t>10 minutes</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
@@ -3122,8 +3146,69 @@
       <c r="T27" s="7" t="inlineStr"/>
       <c r="U27" s="7" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>WF-006</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>step-3</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>File &amp; Close</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>File the witness statement and close. No disciplinary measures or parent notification are required for the witness.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>5 minutes</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr"/>
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr"/>
+      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+      <c r="S28" s="5" t="inlineStr"/>
+      <c r="T28" s="5" t="inlineStr"/>
+      <c r="U28" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U27"/>
+  <autoFilter ref="A1:U28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -1929,12 +1929,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Safety Coordinator &amp; Administration Alert</t>
+          <t>Submit Incident Report</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Notify safety coordinator and school administration; for illegal substances or weapons, notify law enforcement</t>
+          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1967,26 +1967,10 @@
       <c r="M11" s="7" t="inlineStr"/>
       <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr"/>
       <c r="T11" s="7" t="inlineStr"/>
       <c r="U11" s="7" t="inlineStr"/>
     </row>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
+          <t>Driver submits the incident details — what occurred, the prohibited item involved, and how it was confiscated or secured — through the tablet app. Submitting the report notifies the safety coordinator.</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incident Types'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflows'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$K$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Email Templates'!$A$1:$H$4</definedName>
   </definedNames>
@@ -1171,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -3069,130 +3069,8 @@
       <c r="T26" s="5" t="inlineStr"/>
       <c r="U26" s="5" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>WF-006</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>step-2</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Link to Related Incident</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>Safety coordinator reviews the statement and links it to the related disciplinary incident (e.g. the physical altercation) for context.</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>Safety Coordinator</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>10 minutes</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr"/>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr"/>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-      <c r="O27" s="7" t="inlineStr"/>
-      <c r="P27" s="7" t="inlineStr"/>
-      <c r="Q27" s="7" t="inlineStr"/>
-      <c r="R27" s="7" t="inlineStr"/>
-      <c r="S27" s="7" t="inlineStr"/>
-      <c r="T27" s="7" t="inlineStr"/>
-      <c r="U27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>WF-006</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>step-3</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>File &amp; Close</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>File the witness statement and close. No disciplinary measures or parent notification are required for the witness.</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Safety Coordinator</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>5 minutes</t>
-        </is>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr"/>
-      <c r="N28" s="5" t="inlineStr"/>
-      <c r="O28" s="5" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
-      <c r="R28" s="5" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr"/>
-      <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:U28"/>
+  <autoFilter ref="A1:U26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incident Types'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflows'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$K$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$N$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Email Templates'!$A$1:$H$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3081,7 +3081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3094,7 +3094,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3150,6 +3153,21 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>notify_approvers</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>notify_groups</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>email_template</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
           <t>tags</t>
         </is>
       </c>
@@ -3192,12 +3210,12 @@
       </c>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -3205,7 +3223,10 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr"/>
+      <c r="L2" s="5" t="inlineStr"/>
+      <c r="M2" s="5" t="inlineStr"/>
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>parent, guardian, notification, contact</t>
         </is>
@@ -3262,7 +3283,10 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>safety, coordinator, alert, urgent</t>
         </is>
@@ -3319,7 +3343,10 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>administrator, principal, school, notification</t>
         </is>
@@ -3364,7 +3391,10 @@
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>photo, evidence, documentation, damage</t>
         </is>
@@ -3408,7 +3438,7 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
@@ -3422,6 +3452,21 @@
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>disciplinary, review, administrator, approval</t>
         </is>
@@ -3478,7 +3523,10 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>police, law enforcement, criminal, report</t>
         </is>
@@ -3520,10 +3568,37 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>fleet, repair, vehicle, damage, maintenance</t>
         </is>
@@ -3565,29 +3640,20 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr">
         <is>
           <t>close, documentation, finalize, complete</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K9"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Driver submits the incident details — what occurred, injuries, and any threatening behavior — through the tablet app. Submitting the report notifies the safety coordinator.</t>
+          <t>Driver submits the incident details — what occurred, the safety violation involved, and any action taken to secure the situation — through the tablet app. Submitting the report notifies the safety coordinator.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Incident Types'!$A$1:$F$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Workflows'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Workflow Steps'!$A$1:$U$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Step Templates'!$A$1:$N$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Email Templates'!$A$1:$H$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3081,7 +3081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3235,32 +3235,32 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>comm-safety-alert</t>
+          <t>doc-photo-evidence</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>Safety Coordinator Alert</t>
+          <t>Photo &amp; Evidence Documentation</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Review &amp; Action</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Send urgent notification to safety coordinator with full incident details</t>
+          <t>Photograph damage or relevant scene, document physical evidence</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Safety Coordinator</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>15 minutes</t>
+          <t>20 minutes</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -3268,74 +3268,62 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="H3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>safety, coordinator, alert, urgent</t>
+          <t>photo, evidence, documentation, damage</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>comm-admin-notify</t>
+          <t>admin-disciplinary-review</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Administrator / Principal Notification</t>
+          <t>Disciplinary Review</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Review &amp; Action</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Notify school administrator or principal of the incident</t>
+          <t>Administrator reviews incident and determines appropriate disciplinary action; requires approval before proceeding</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>School Principal</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>20 minutes</t>
+          <t>1 hour</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
@@ -3343,24 +3331,36 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Safety Coordinator</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>administrator, principal, school, notification</t>
+          <t>disciplinary, review, administrator, approval</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>doc-photo-evidence</t>
+          <t>admin-police-report</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Photo &amp; Evidence Documentation</t>
+          <t>Law Enforcement Contact</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -3370,290 +3370,98 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Photograph damage or relevant scene, document physical evidence</t>
+          <t>File police report or coordinate with law enforcement for criminal incidents</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Driver</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>20 minutes</t>
+          <t>1 hour</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>photo, evidence, documentation, damage</t>
+          <t>police, law enforcement, criminal, report</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>admin-disciplinary-review</t>
+          <t>follow-close-incident</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Disciplinary Review</t>
+          <t>Documentation &amp; Close</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Review &amp; Action</t>
+          <t>Close Out</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Administrator reviews incident and determines appropriate disciplinary action; requires approval before proceeding</t>
+          <t>Complete all incident documentation, finalize the record, and close the case</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Safety Coordinator</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>1 hour</t>
+          <t>15 minutes</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Safety Coordinator</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr">
         <is>
-          <t>disciplinary, review, administrator, approval</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>admin-police-report</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Law Enforcement Contact</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Review &amp; Action</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>File police report or coordinate with law enforcement for criminal incidents</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Administrator</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>1 hour</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>police, law enforcement, criminal, report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>admin-fleet-repair</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Fleet / Repair Coordination</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Review &amp; Action</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Fleet manager assesses damage, provides repair estimate, and schedules vehicle repairs</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Fleet Manager</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>2 hours</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Safety Coordinator</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>fleet, repair, vehicle, damage, maintenance</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>follow-close-incident</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Documentation &amp; Close</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Close Out</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>Complete all incident documentation, finalize the record, and close the case</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Safety Coordinator</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>15 minutes</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
           <t>close, documentation, finalize, complete</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -3303,7 +3303,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>School Principal</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">

--- a/Incident-Tracker-Seed-Catalog.xlsx
+++ b/Incident-Tracker-Seed-Catalog.xlsx
@@ -3388,21 +3388,9 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="J5" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+      <c r="H5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="7" t="inlineStr"/>
       <c r="L5" s="7" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
